--- a/Proiect/Proiect/Output/Date/Date_Testare.xlsx
+++ b/Proiect/Proiect/Output/Date/Date_Testare.xlsx
@@ -434,197 +434,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Croația</t>
         </is>
       </c>
       <c r="B2">
         <v>2023</v>
       </c>
       <c r="C2">
-        <v>26153</v>
+        <v>11270</v>
       </c>
       <c r="D2">
-        <v>10950</v>
+        <v>16490</v>
       </c>
       <c r="E2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F2">
-        <v>56807</v>
+        <v>69396</v>
       </c>
       <c r="G2">
-        <v>29120</v>
+        <v>20333</v>
       </c>
       <c r="H2">
-        <v>58.6</v>
+        <v>69</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>10.17171918566626</v>
+        <v>9.329899607033822</v>
       </c>
       <c r="K2">
-        <v>9.301094735244646</v>
+        <v>9.710509415553645</v>
       </c>
       <c r="L2">
-        <v>4.882801922586371</v>
+        <v>4.663439094112067</v>
       </c>
       <c r="M2">
-        <v>10.94743243986193</v>
+        <v>11.14759891789485</v>
       </c>
       <c r="N2">
-        <v>10.27918050231062</v>
+        <v>9.920000460910341</v>
       </c>
       <c r="O2">
-        <v>4.070734696582967</v>
+        <v>4.23410650459726</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Croația</t>
+          <t>Danemarca</t>
         </is>
       </c>
       <c r="B3">
         <v>2023</v>
       </c>
       <c r="C3">
-        <v>11270</v>
+        <v>158491</v>
       </c>
       <c r="D3">
-        <v>16490</v>
+        <v>56470</v>
       </c>
       <c r="E3">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="F3">
-        <v>69396</v>
+        <v>98344</v>
       </c>
       <c r="G3">
-        <v>20333</v>
+        <v>11422</v>
       </c>
       <c r="H3">
-        <v>69</v>
+        <v>141.6</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>9.329899607033822</v>
+        <v>11.97345308835291</v>
       </c>
       <c r="K3">
-        <v>9.710509415553645</v>
+        <v>10.94146480266688</v>
       </c>
       <c r="L3">
-        <v>4.663439094112067</v>
+        <v>5.087596335232384</v>
       </c>
       <c r="M3">
-        <v>11.14759891789485</v>
+        <v>11.49623698368399</v>
       </c>
       <c r="N3">
-        <v>9.920000460910341</v>
+        <v>9.343296599224809</v>
       </c>
       <c r="O3">
-        <v>4.23410650459726</v>
+        <v>4.953006181259619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danemarca</t>
+          <t>Slovacia</t>
         </is>
       </c>
       <c r="B4">
         <v>2023</v>
       </c>
       <c r="C4">
-        <v>158491</v>
+        <v>11826</v>
       </c>
       <c r="D4">
-        <v>56470</v>
+        <v>18750</v>
       </c>
       <c r="E4">
         <v>162</v>
       </c>
       <c r="F4">
-        <v>98344</v>
+        <v>5923</v>
       </c>
       <c r="G4">
-        <v>11422</v>
+        <v>20037</v>
       </c>
       <c r="H4">
-        <v>141.6</v>
+        <v>111.4</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>11.97345308835291</v>
+        <v>9.378055776380775</v>
       </c>
       <c r="K4">
-        <v>10.94146480266688</v>
+        <v>9.838949031398556</v>
       </c>
       <c r="L4">
         <v>5.087596335232384</v>
       </c>
       <c r="M4">
-        <v>11.49623698368399</v>
+        <v>8.68676717538769</v>
       </c>
       <c r="N4">
-        <v>9.343296599224809</v>
+        <v>9.905335843393745</v>
       </c>
       <c r="O4">
-        <v>4.953006181259619</v>
+        <v>4.713127327493184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Suedia</t>
         </is>
       </c>
       <c r="B5">
         <v>2023</v>
       </c>
       <c r="C5">
-        <v>117183</v>
+        <v>287940</v>
       </c>
       <c r="D5">
-        <v>15950</v>
+        <v>47960</v>
       </c>
       <c r="E5">
-        <v>502</v>
+        <v>440</v>
       </c>
       <c r="F5">
-        <v>303275</v>
+        <v>94514</v>
       </c>
       <c r="G5">
-        <v>96698</v>
+        <v>22980</v>
       </c>
       <c r="H5">
-        <v>119.4</v>
+        <v>25.9</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>11.67149209440957</v>
+        <v>12.57050740408035</v>
       </c>
       <c r="K5">
-        <v>9.67721410821299</v>
+        <v>10.77812260914145</v>
       </c>
       <c r="L5">
-        <v>6.218600119691729</v>
+        <v>6.086774726912306</v>
       </c>
       <c r="M5">
-        <v>12.62239856097108</v>
+        <v>11.45651383104427</v>
       </c>
       <c r="N5">
-        <v>11.47934799870423</v>
+        <v>10.04237955140275</v>
       </c>
       <c r="O5">
-        <v>4.782479200958502</v>
+        <v>3.254242968705492</v>
       </c>
     </row>
   </sheetData>

--- a/Proiect/Proiect/Output/Date/Date_Testare.xlsx
+++ b/Proiect/Proiect/Output/Date/Date_Testare.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,243 +387,328 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Politie</t>
+          <t>Densitate_Populatie</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Densitate_Populatie</t>
+          <t>Est_Vest</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Membru_UE</t>
+          <t>ln_Furturi</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ln_Furturi</t>
+          <t>ln_PIB</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>ln_PIB</t>
+          <t>ln_Someri</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ln_Someri</t>
+          <t>ln_Imigratie</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ln_Imigratie</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ln_Politie</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ln_Densitate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Croația</t>
-        </is>
-      </c>
       <c r="B2">
         <v>2023</v>
       </c>
       <c r="C2">
-        <v>11270</v>
+        <v>9699</v>
       </c>
       <c r="D2">
-        <v>16490</v>
+        <v>21210</v>
       </c>
       <c r="E2">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="F2">
-        <v>69396</v>
+        <v>26399</v>
       </c>
       <c r="G2">
-        <v>20333</v>
+        <v>31.8</v>
       </c>
       <c r="H2">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>9.179778066393542</v>
       </c>
       <c r="J2">
-        <v>9.329899607033822</v>
+        <v>9.962228047558728</v>
       </c>
       <c r="K2">
-        <v>9.710509415553645</v>
+        <v>3.871201010907891</v>
       </c>
       <c r="L2">
-        <v>4.663439094112067</v>
+        <v>10.18111928913441</v>
       </c>
       <c r="M2">
-        <v>11.14759891789485</v>
-      </c>
-      <c r="N2">
-        <v>9.920000460910341</v>
-      </c>
-      <c r="O2">
-        <v>4.23410650459726</v>
+        <v>3.459466289786131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Danemarca</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B3">
         <v>2023</v>
       </c>
       <c r="C3">
-        <v>158491</v>
+        <v>68659</v>
       </c>
       <c r="D3">
-        <v>56470</v>
+        <v>18600</v>
       </c>
       <c r="E3">
-        <v>162</v>
+        <v>522</v>
       </c>
       <c r="F3">
-        <v>98344</v>
+        <v>118816</v>
       </c>
       <c r="G3">
-        <v>11422</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>141.6</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11.13690750238479</v>
       </c>
       <c r="J3">
-        <v>11.97345308835291</v>
+        <v>9.830916859701293</v>
       </c>
       <c r="K3">
-        <v>10.94146480266688</v>
+        <v>6.257667587882639</v>
       </c>
       <c r="L3">
-        <v>5.087596335232384</v>
+        <v>11.68533977331629</v>
       </c>
       <c r="M3">
-        <v>11.49623698368399</v>
-      </c>
-      <c r="N3">
-        <v>9.343296599224809</v>
-      </c>
-      <c r="O3">
-        <v>4.953006181259619</v>
+        <v>4.382026634673881</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Slovacia</t>
+          <t>Ungaria</t>
         </is>
       </c>
       <c r="B4">
         <v>2023</v>
       </c>
       <c r="C4">
-        <v>11826</v>
+        <v>50934</v>
       </c>
       <c r="D4">
-        <v>18750</v>
+        <v>16050</v>
       </c>
       <c r="E4">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="F4">
-        <v>5923</v>
+        <v>96192</v>
       </c>
       <c r="G4">
-        <v>20037</v>
+        <v>105.1</v>
       </c>
       <c r="H4">
-        <v>111.4</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>10.83828595596602</v>
       </c>
       <c r="J4">
-        <v>9.378055776380775</v>
+        <v>9.683464128558162</v>
       </c>
       <c r="K4">
-        <v>9.838949031398556</v>
+        <v>5.303304908059076</v>
       </c>
       <c r="L4">
-        <v>5.087596335232384</v>
+        <v>11.47411186893353</v>
       </c>
       <c r="M4">
-        <v>8.68676717538769</v>
-      </c>
-      <c r="N4">
-        <v>9.905335843393745</v>
-      </c>
-      <c r="O4">
-        <v>4.713127327493184</v>
+        <v>4.654912277882906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Suedia</t>
+          <t>Islanda</t>
         </is>
       </c>
       <c r="B5">
         <v>2023</v>
       </c>
       <c r="C5">
+        <v>3629</v>
+      </c>
+      <c r="D5">
+        <v>61180</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>11235</v>
+      </c>
+      <c r="G5">
+        <v>3.8</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>8.19671240721307</v>
+      </c>
+      <c r="J5">
+        <v>11.02157561770489</v>
+      </c>
+      <c r="K5">
+        <v>2.079441541679836</v>
+      </c>
+      <c r="L5">
+        <v>9.326878188224134</v>
+      </c>
+      <c r="M5">
+        <v>1.33500106673234</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Irlanda</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="C6">
+        <v>69354</v>
+      </c>
+      <c r="D6">
+        <v>87810</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="F6">
+        <v>135617</v>
+      </c>
+      <c r="G6">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>11.14697910252232</v>
+      </c>
+      <c r="J6">
+        <v>11.38293066835404</v>
+      </c>
+      <c r="K6">
+        <v>4.787491742782046</v>
+      </c>
+      <c r="L6">
+        <v>11.81759738904164</v>
+      </c>
+      <c r="M6">
+        <v>4.348986780595681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <v>2023</v>
+      </c>
+      <c r="C7">
+        <v>14783</v>
+      </c>
+      <c r="D7">
+        <v>8510</v>
+      </c>
+      <c r="E7">
+        <v>296</v>
+      </c>
+      <c r="F7">
+        <v>203644.0857142857</v>
+      </c>
+      <c r="G7">
+        <v>90.5</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>9.60123315090109</v>
+      </c>
+      <c r="J7">
+        <v>9.04899722156742</v>
+      </c>
+      <c r="K7">
+        <v>5.69035945432406</v>
+      </c>
+      <c r="L7">
+        <v>12.22413398174826</v>
+      </c>
+      <c r="M7">
+        <v>4.505349850705881</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Suedia</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2023</v>
+      </c>
+      <c r="C8">
         <v>287940</v>
       </c>
-      <c r="D5">
+      <c r="D8">
         <v>47960</v>
       </c>
-      <c r="E5">
+      <c r="E8">
         <v>440</v>
       </c>
-      <c r="F5">
+      <c r="F8">
         <v>94514</v>
       </c>
-      <c r="G5">
-        <v>22980</v>
-      </c>
-      <c r="H5">
+      <c r="G8">
         <v>25.9</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>12.57050740408035</v>
       </c>
-      <c r="K5">
+      <c r="J8">
         <v>10.77812260914145</v>
       </c>
-      <c r="L5">
+      <c r="K8">
         <v>6.086774726912306</v>
       </c>
-      <c r="M5">
+      <c r="L8">
         <v>11.45651383104427</v>
       </c>
-      <c r="N5">
-        <v>10.04237955140275</v>
-      </c>
-      <c r="O5">
+      <c r="M8">
         <v>3.254242968705492</v>
       </c>
     </row>
